--- a/config/excel/game_tuning.xlsx
+++ b/config/excel/game_tuning.xlsx
@@ -423,12 +423,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>390</v>
+        <v>720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>700</v>
+        <v>1280</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -496,7 +496,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>camera_zoom</t>
+          <t>world_scale</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -504,320 +504,320 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>战斗镜头缩放(1=正常，勿随意改大)</t>
+          <t>世界比例微调(乘在分辨率比例后)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>monster_sprite_scale</t>
+          <t>ui_scale</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>怪物显示缩放</t>
+          <t>界面比例微调(乘在分辨率比例后)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bullet_time_scale</t>
+          <t>camera_zoom</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.14</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>子弹时间缩放</t>
+          <t>战斗镜头缩放(1=正常，勿随意改大)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bullet_time_dim_alpha</t>
+          <t>monster_sprite_scale</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.42</v>
+        <v>3.7</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>子弹时间暗化</t>
+          <t>怪物显示缩放</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>stages_per_chapter</t>
+          <t>bullet_time_scale</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>0.14</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>每章关卡数</t>
+          <t>子弹时间缩放</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>stage_hp_growth</t>
+          <t>bullet_time_dim_alpha</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.2</v>
+        <v>0.42</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>关卡HP缩放幂次</t>
+          <t>子弹时间暗化</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>stage_def_growth</t>
+          <t>stages_per_chapter</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>关卡DEF缩放幂次</t>
+          <t>每章关卡数</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>stage_monster_scale</t>
+          <t>stage_hp_growth</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>关卡怪物数量缩放</t>
+          <t>关卡HP缩放幂次</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>stage_count_mul</t>
+          <t>stage_def_growth</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.666667</v>
+        <v>1.1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>怪物数量乘数</t>
+          <t>关卡DEF缩放幂次</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>shield_count_mul</t>
+          <t>stage_monster_scale</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.333333</v>
+        <v>1.3</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>盾牌怪数量乘数</t>
+          <t>关卡怪物数量缩放</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>exp_base_to_level</t>
+          <t>stage_count_mul</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>100</v>
+        <v>0.666667</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>升级所需基础经验</t>
+          <t>怪物数量乘数</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>exp_growth</t>
+          <t>shield_count_mul</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.22</v>
+        <v>0.333333</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>升级经验增长</t>
+          <t>盾牌怪数量乘数</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>terrain_folder</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Terrain</t>
-        </is>
+          <t>exp_base_to_level</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>50</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>地形素材目录</t>
+          <t>升级所需基础经验</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ui_folder</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ui</t>
-        </is>
+          <t>exp_growth</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UI素材目录</t>
+          <t>升级经验增长</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>effects_folder</t>
+          <t>terrain_folder</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>effects</t>
+          <t>Terrain</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>特效素材目录</t>
+          <t>地形素材目录</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fire_pillar_radius</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>60</v>
+          <t>ui_folder</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ui</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>火柱半径</t>
+          <t>UI素材目录</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fire_pillar_warning_time</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1.1</v>
+          <t>effects_folder</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>effects</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>火柱预警时间</t>
+          <t>特效素材目录</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fire_pillar_active_time</t>
+          <t>fire_pillar_radius</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5</v>
+        <v>60</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>火柱持续时间</t>
+          <t>火柱半径</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fire_pillar_fade_time</t>
+          <t>fire_pillar_warning_time</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>火柱淡出时间</t>
+          <t>火柱预警时间</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>stage_intro_slide_in</t>
+          <t>fire_pillar_active_time</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>关卡 intro 滑入时长</t>
+          <t>火柱持续时间</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>stage_intro_hold</t>
+          <t>fire_pillar_fade_time</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.85</v>
+        <v>0.3</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>关卡 intro 停留时长</t>
+          <t>火柱淡出时间</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>stage_intro_slide_out</t>
+          <t>stage_intro_slide_in</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -825,209 +825,209 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>关卡 intro 滑出时长</t>
+          <t>关卡 intro 滑入时长</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>stage_intro_sakura_extra</t>
+          <t>stage_intro_hold</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>intro 樱花额外停留</t>
+          <t>关卡 intro 停留时长</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>stage_clear_flash_duration</t>
+          <t>stage_intro_slide_out</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.1</v>
+        <v>0.38</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>过关闪白时长</t>
+          <t>关卡 intro 滑出时长</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>stage_fail_label_duration</t>
+          <t>stage_intro_sakura_extra</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>失败字幕时长</t>
+          <t>intro 樱花额外停留</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>stage_fail_overlay_fade</t>
+          <t>stage_clear_flash_duration</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.65</v>
+        <v>1.1</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>失败遮罩淡入时长</t>
+          <t>过关闪白时长</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>fail_death_windup</t>
+          <t>stage_fail_label_duration</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>失败动画蓄力</t>
+          <t>失败字幕时长</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fail_death_spear_stagger</t>
+          <t>stage_fail_overlay_fade</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.065</v>
+        <v>0.65</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>失败投矛错峰</t>
+          <t>失败遮罩淡入时长</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>fail_death_spear_speed</t>
+          <t>fail_death_windup</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>640</v>
+        <v>0.3</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>失败投矛速度</t>
+          <t>失败动画蓄力</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>fail_death_impact_pause</t>
+          <t>fail_death_spear_stagger</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.24</v>
+        <v>0.065</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>失败插矛停顿</t>
+          <t>失败投矛错峰</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>fail_death_duration</t>
+          <t>fail_death_spear_speed</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9</v>
+        <v>640</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>失败倒地时长</t>
+          <t>失败投矛速度</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>fail_death_playback_speed</t>
+          <t>fail_death_impact_pause</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>0.24</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>失败动画加速</t>
+          <t>失败插矛停顿</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>combat_first_hit_delay</t>
+          <t>fail_death_duration</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.04</v>
+        <v>0.9</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>连击首击延迟</t>
+          <t>失败倒地时长</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>combat_hit_interval</t>
+          <t>fail_death_playback_speed</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.012</v>
+        <v>2</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>连击命中间隔</t>
+          <t>失败动画加速</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>combat_afterimage_life</t>
+          <t>combat_first_hit_delay</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>连击残影寿命</t>
+          <t>连击首击延迟</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>combat_death_stagger</t>
+          <t>combat_hit_interval</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1035,119 +1035,119 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>死亡错峰间隔</t>
+          <t>连击命中间隔</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>monster_spawn_anim</t>
+          <t>combat_afterimage_life</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.42</v>
+        <v>0.1</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>怪物出生动画时长</t>
+          <t>连击残影寿命</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>sakura_petal_count</t>
+          <t>combat_death_stagger</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>42</v>
+        <v>0.012</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>樱花花瓣数量</t>
+          <t>死亡错峰间隔</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>sakura_default_duration</t>
+          <t>monster_spawn_anim</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5.5</v>
+        <v>0.42</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>樱花默认时长</t>
+          <t>怪物出生动画时长</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>sakura_fade_out_duration</t>
+          <t>sakura_petal_count</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.8</v>
+        <v>42</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>樱花淡出时长</t>
+          <t>樱花花瓣数量</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>grass_cluster_max</t>
+          <t>sakura_default_duration</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>22</v>
+        <v>5.5</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>草簇最大数量</t>
+          <t>樱花默认时长</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>terrain_prop_count</t>
+          <t>sakura_fade_out_duration</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>8</v>
+        <v>1.8</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>地形装饰数量</t>
+          <t>樱花淡出时长</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>target_fps</t>
+          <t>grass_cluster_max</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>目标帧率(0=不限制)</t>
+          <t>草簇最大数量</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>stage_monster_base</t>
+          <t>terrain_prop_count</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1155,52 +1155,337 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>第1关怪物总数（stages表为权威）</t>
+          <t>地形装饰数量</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>stage_monster_per_stage</t>
+          <t>target_fps</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>每过一关怪物总数+1</t>
+          <t>目标帧率(0=不限制)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>stage_type_unlock_interval</t>
+          <t>stage_monster_base</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>每N关解锁下一种怪物</t>
+          <t>第1关怪物总数（stages表为权威）</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>stage_monster_per_stage</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>每过一关怪物总数+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>stage_atk_growth</t>
         </is>
       </c>
-      <c r="B51" t="n">
+      <c r="B52" t="n">
         <v>1.12</v>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>关卡攻击缩放幂次</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>monster_speed_mul</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>怪物移速全局倍率</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>damage_formula_version</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>伤害公式版本(1=旧:raw-def, 2=新:分层乘区)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>def_softening_K_base</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>100</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>新公式防御软化系数基础值(K_base, K=base+per_stage*stage_idx)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>def_softening_K_per_stage</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>20</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>新公式防御软化系数每关增量</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>crit_soft_cap_threshold</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>暴击率软上限阈值(超过此值后递减逼近95%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>dot_tick_floor_seconds</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DoT 每目标最小 tick 间隔(防全屏燃烧爆炸)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>stage_duration_sec</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>120</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>每关战斗倒计时秒数</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>infinite_spawn_interval</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>倒计时模式下相邻怪物的出现间隔(秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>infinite_spawn_wave_delay</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>倒计时模式下整批刷完后等待下一批的间隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>wood_per_block</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>20</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>盖房子阶段木材→木块兑换比例</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>house_block_size_m</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>盖房子木块边长(米)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>house_px_per_meter</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>36</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>盖房子阶段每米对应像素数(2m=72px)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>house_swing_speed</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>盖房子绳子摆动角速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>house_swing_amplitude_px</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>180</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>盖房子绳子摆动幅度(像素)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>portal_chance_per_tick</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>抽奖传送门每1.5s概率</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>portal_lifetime_sec</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>5</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>抽奖传送门存在时长</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>tree_count_per_wave</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>5</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>每波刷新树木数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>tree_hp</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>450</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>单棵树血量(目标约 4-5 次斩击全砍)</t>
         </is>
       </c>
     </row>
